--- a/example_folder/velocity.xlsx
+++ b/example_folder/velocity.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\test_pp\example_folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\pptx_velocity\example_folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BDBE2A-5A01-45A3-BD9C-44EDB3D54D78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D66170-8C83-4F7E-B225-3B98F5E0973D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{7F9A0932-A938-409A-B453-E824913297A1}"/>
+    <workbookView xWindow="10620" yWindow="2570" windowWidth="25850" windowHeight="17230" activeTab="1" xr2:uid="{7F9A0932-A938-409A-B453-E824913297A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -23,7 +28,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>sku</t>
   </si>
@@ -40,13 +48,80 @@
   </si>
   <si>
     <t>ros</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>change</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>3 slide</t>
+  </si>
+  <si>
+    <t>1/2 slide</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>ND, LM</t>
+  </si>
+  <si>
+    <t>Рейтинг</t>
+  </si>
+  <si>
+    <t>Изм vs. LY</t>
+  </si>
+  <si>
+    <t>Продажи на ТТ</t>
+  </si>
+  <si>
+    <t>Микс цена</t>
+  </si>
+  <si>
+    <t>4 категории</t>
+  </si>
+  <si>
+    <t xml:space="preserve">А4 ориентация </t>
+  </si>
+  <si>
+    <t>положительный -  зеленый, отрицательный - красный</t>
+  </si>
+  <si>
+    <t>медиана - линией</t>
+  </si>
+  <si>
+    <t>и шрифт Calibri</t>
+  </si>
+  <si>
+    <t>SizeX</t>
+  </si>
+  <si>
+    <t>SizeY</t>
+  </si>
+  <si>
+    <t>Cat Two</t>
+  </si>
+  <si>
+    <t>Cat Three</t>
+  </si>
+  <si>
+    <t>Category One Number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,16 +130,333 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -72,16 +464,229 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="45">
+    <cellStyle name="20% - Accent1 2" xfId="21" xr:uid="{25DCE82B-8622-487F-A804-B0A0548C9AF6}"/>
+    <cellStyle name="20% - Accent2 2" xfId="25" xr:uid="{9E256BA8-0562-4E2E-BFA1-F6BE8395CF0C}"/>
+    <cellStyle name="20% - Accent3 2" xfId="29" xr:uid="{EB3E298F-9AFC-49C2-82A3-534F3A835BAB}"/>
+    <cellStyle name="20% - Accent4 2" xfId="33" xr:uid="{66347714-20A4-47B2-AD14-BB3E95C3BE0D}"/>
+    <cellStyle name="20% - Accent5 2" xfId="37" xr:uid="{75544610-7C7A-403A-951A-0E44C9A368DD}"/>
+    <cellStyle name="20% - Accent6 2" xfId="41" xr:uid="{1150A7B9-0FDE-42E6-90A6-55F9CDEF0899}"/>
+    <cellStyle name="40% - Accent1 2" xfId="22" xr:uid="{4150C4E9-541F-4151-B3F9-90BDA97387E4}"/>
+    <cellStyle name="40% - Accent2 2" xfId="26" xr:uid="{86D4FADE-D9E5-4E78-958F-1F2FD7BD52E4}"/>
+    <cellStyle name="40% - Accent3 2" xfId="30" xr:uid="{88476275-059F-4981-838D-2A4739E4F445}"/>
+    <cellStyle name="40% - Accent4 2" xfId="34" xr:uid="{F606418F-6465-4B19-B4C5-8049A729F4D1}"/>
+    <cellStyle name="40% - Accent5 2" xfId="38" xr:uid="{025F0A58-8DE7-424A-8C4E-9979899513F9}"/>
+    <cellStyle name="40% - Accent6 2" xfId="42" xr:uid="{4A58A2E3-DCB8-46B6-9C8C-6B623471F8BD}"/>
+    <cellStyle name="60% - Accent1 2" xfId="23" xr:uid="{17000CF8-AD9C-4E02-A1A8-5A775A38DFAA}"/>
+    <cellStyle name="60% - Accent2 2" xfId="27" xr:uid="{8A2440D1-AB4D-4C9E-8CF7-084332861776}"/>
+    <cellStyle name="60% - Accent3 2" xfId="31" xr:uid="{BEABD10E-BBDE-4AE9-91D2-1F06ADAE553A}"/>
+    <cellStyle name="60% - Accent4 2" xfId="35" xr:uid="{07431290-B897-4B1D-A097-E8F22F3C6010}"/>
+    <cellStyle name="60% - Accent5 2" xfId="39" xr:uid="{D0B7FD14-DCBB-49BF-B779-2B748A76E778}"/>
+    <cellStyle name="60% - Accent6 2" xfId="43" xr:uid="{DB5F516B-DF14-400D-B568-9FC6A0CEF00D}"/>
+    <cellStyle name="Accent1 2" xfId="20" xr:uid="{5CBBFF68-1372-4AD8-B831-0A9DB1D6E990}"/>
+    <cellStyle name="Accent2 2" xfId="24" xr:uid="{36D972CA-7F9E-4379-A170-CD37E74536B7}"/>
+    <cellStyle name="Accent3 2" xfId="28" xr:uid="{7205B7D3-5A1E-4565-AD08-14416DE01C63}"/>
+    <cellStyle name="Accent4 2" xfId="32" xr:uid="{DBD0050A-CEED-4096-80C7-71BE230E834A}"/>
+    <cellStyle name="Accent5 2" xfId="36" xr:uid="{00888F68-426A-4A55-BD67-2CEC1A8278C4}"/>
+    <cellStyle name="Accent6 2" xfId="40" xr:uid="{25FEB26A-DB1E-4DBE-8526-95010608A5D6}"/>
+    <cellStyle name="Bad 2" xfId="10" xr:uid="{CC34E4D6-782B-4C92-92C6-F3A7A0E1CA64}"/>
+    <cellStyle name="Calculation 2" xfId="14" xr:uid="{687C7A3C-3367-4CF1-87E2-7A1D4D578349}"/>
+    <cellStyle name="Check Cell 2" xfId="16" xr:uid="{2A025CD6-6A64-4FA4-B144-C880548768DB}"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Explanatory Text 2" xfId="18" xr:uid="{60862532-5A47-4FCE-AD09-458FFB1B0B42}"/>
+    <cellStyle name="Good 2" xfId="9" xr:uid="{04352ED8-3E7F-4A76-AD4F-545DE2F2079A}"/>
+    <cellStyle name="Heading 1 2" xfId="5" xr:uid="{5DD3DC75-5CF2-4A99-BF1C-046A622EDE12}"/>
+    <cellStyle name="Heading 2 2" xfId="6" xr:uid="{FF3765E8-BF6B-4120-AC95-56C7BCDF5AA1}"/>
+    <cellStyle name="Heading 3 2" xfId="7" xr:uid="{06149C31-CF2A-41C1-B701-3B2E3E564EFF}"/>
+    <cellStyle name="Heading 4 2" xfId="8" xr:uid="{FF3E3417-32D6-49E1-ACEB-5C6788073F05}"/>
+    <cellStyle name="Input 2" xfId="12" xr:uid="{DA009A81-031E-4560-90FD-81B6B0C547FD}"/>
+    <cellStyle name="Linked Cell 2" xfId="15" xr:uid="{E09B42BC-9A83-4990-A447-A1AD6E830799}"/>
+    <cellStyle name="Neutral 2" xfId="11" xr:uid="{F925748B-2A7A-46B6-A9A0-812F6DEB7313}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="44" xr:uid="{2BE781D6-2F44-4B07-85E7-C6D0D9D5F79E}"/>
+    <cellStyle name="Note" xfId="3" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output 2" xfId="13" xr:uid="{139A908B-8C0F-494D-9C1C-FA9BCB59D3F8}"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Title 2" xfId="4" xr:uid="{FE43725C-0E02-4093-A370-5BB0060E39A1}"/>
+    <cellStyle name="Total 2" xfId="19" xr:uid="{F25749A7-310C-4A4C-BEA2-B5C0FE056C5C}"/>
+    <cellStyle name="Warning Text 2" xfId="17" xr:uid="{59228871-EE83-4511-A520-9A65301AB7BE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -97,9 +702,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +742,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -243,7 +848,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -385,7 +990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -393,181 +998,789 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA24C5F5-9985-4192-8ECE-0DE54C9E7913}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="10.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>110040926</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.12291169451073986</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1363.4367960312404</v>
+      </c>
+      <c r="D2" s="2">
+        <v>28</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>110041170</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.11971143415057496</v>
+      </c>
+      <c r="C3" s="3">
+        <v>836.26692971481486</v>
+      </c>
+      <c r="D3" s="2">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>110040924</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.28645042308526797</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1065.751730162855</v>
+      </c>
+      <c r="D4" s="2">
+        <v>25</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>110040913</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.17899761336515513</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1662.0162823293679</v>
+      </c>
+      <c r="D5" s="2">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>110040917</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.40648730744196138</v>
+      </c>
+      <c r="C6" s="3">
+        <v>835.87593554764192</v>
+      </c>
+      <c r="D6" s="2">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>-32</v>
+      </c>
+      <c r="F6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>110040909</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.40702972445215879</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1584.2590365125307</v>
+      </c>
+      <c r="D7" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>110040910</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.2962139292688219</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1590.7125265110171</v>
+      </c>
+      <c r="D8" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>-34</v>
+      </c>
+      <c r="F8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>110040920</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.24235192015621609</v>
+      </c>
+      <c r="C9" s="3">
+        <v>895.72597079045806</v>
+      </c>
+      <c r="D9" s="2">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>110040919</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.33939032328053809</v>
+      </c>
+      <c r="C10" s="3">
+        <v>402.03351024071986</v>
+      </c>
+      <c r="D10" s="2">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>-21</v>
+      </c>
+      <c r="F10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>110040907</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.41391842048166633</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2516.893424891728</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>110041171</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.15507702321544803</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1222.5802496916644</v>
+      </c>
+      <c r="D12" s="2">
+        <v>26</v>
+      </c>
+      <c r="E12">
+        <v>42</v>
+      </c>
+      <c r="F12">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>110040929</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.14520503362985462</v>
+      </c>
+      <c r="C13" s="3">
+        <v>659.58116552906745</v>
+      </c>
+      <c r="D13" s="2">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>110040921</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.28021262746799741</v>
+      </c>
+      <c r="C14" s="3">
+        <v>681.20510975548871</v>
+      </c>
+      <c r="D14" s="2">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>-12</v>
+      </c>
+      <c r="F14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>110040921</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.16597960512041657</v>
+      </c>
+      <c r="C15" s="3">
+        <v>466.47094581249468</v>
+      </c>
+      <c r="D15" s="2">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>-46</v>
+      </c>
+      <c r="F15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>110040917</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.5571707528748101</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1209.4766041853156</v>
+      </c>
+      <c r="D16" s="2">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>37</v>
+      </c>
+      <c r="F16">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>110040914</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.254447819483619</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1336.6517362254308</v>
+      </c>
+      <c r="D17" s="2">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>110040909</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.47439791711868085</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2026.03439992775</v>
+      </c>
+      <c r="D18" s="2">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>-2</v>
+      </c>
+      <c r="F18">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>110040911</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.11103276198741592</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2095.3288041882493</v>
+      </c>
+      <c r="D19" s="2">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>110040910</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.22184855717075289</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1763.5963713404101</v>
+      </c>
+      <c r="D20" s="2">
+        <v>28</v>
+      </c>
+      <c r="E20">
+        <v>-42</v>
+      </c>
+      <c r="F20">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>110040911</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.40247342156650034</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1480.6174944335469</v>
+      </c>
+      <c r="D21" s="2">
+        <v>27</v>
+      </c>
+      <c r="E21">
+        <v>-41</v>
+      </c>
+      <c r="F21">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>110040922</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.39157083966153178</v>
+      </c>
+      <c r="C22" s="3">
+        <v>493.14168141524834</v>
+      </c>
+      <c r="D22" s="2">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>-18</v>
+      </c>
+      <c r="F22">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>110040908</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.45438272944239533</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2439.6215754081127</v>
+      </c>
+      <c r="D23" s="2">
+        <v>29</v>
+      </c>
+      <c r="E23">
+        <v>-27</v>
+      </c>
+      <c r="F23">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>110040912</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.40307008027771751</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1806.1269861497785</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>39</v>
+      </c>
+      <c r="F24">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>110040907</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.56888696029507491</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2990.0196499834842</v>
+      </c>
+      <c r="D25" s="2">
+        <v>23</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>110041172</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.47174007376871341</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1104.6787064329867</v>
+      </c>
+      <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>110041173</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.46745497938815361</v>
+      </c>
+      <c r="C27" s="3">
+        <v>974.96743790872767</v>
+      </c>
+      <c r="D27" s="2">
+        <v>27</v>
+      </c>
+      <c r="E27">
+        <v>-30</v>
+      </c>
+      <c r="F27">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{DA24C5F5-9985-4192-8ECE-0DE54C9E7913}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FD2514-273B-493D-B70B-7523724E4163}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>100001</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <f ca="1">RANDBETWEEN(0,100)&amp;"%"</f>
-        <v>71%</v>
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C7" ca="1" si="0">RANDBETWEEN(0,1100)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>100002</v>
-      </c>
-      <c r="B3" s="1" t="str">
-        <f t="shared" ref="B3:B7" ca="1" si="1">RANDBETWEEN(0,100)&amp;"%"</f>
-        <v>60%</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ca="1" si="0"/>
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>100003</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>86%</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ca="1" si="0"/>
-        <v>493</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>100004</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>43%</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ca="1" si="0"/>
-        <v>716</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B41" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7598CE0-6D5C-4D45-874F-01F5CBB14DE6}">
+  <dimension ref="B4:L17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>110040926</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.12291169451073986</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1363.4367960312404</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>110041170</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.11971143415057496</v>
+      </c>
+      <c r="D8" s="3">
+        <v>836.26692971481486</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>110040924</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.28645042308526797</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1065.751730162855</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10">
+        <v>110040913</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.17899761336515513</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1662.0162823293679</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <v>110040917</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.40648730744196138</v>
+      </c>
+      <c r="D11" s="3">
+        <v>835.87593554764192</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B12">
+        <v>110040909</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.40702972445215879</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1584.2590365125307</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.35">
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>